--- a/ECMAC.xlsx
+++ b/ECMAC.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="87">
   <si>
     <t/>
   </si>
@@ -88,13 +88,22 @@
     <t>PT,(E-4B)</t>
   </si>
   <si>
+    <t>20141718</t>
+  </si>
+  <si>
+    <t>DUREX LUBESTRBRY50ML</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
     <t>20131512</t>
   </si>
   <si>
     <t>SUTRA LUBRCNT GEL 50</t>
   </si>
   <si>
-    <t>7</t>
+    <t>8</t>
   </si>
   <si>
     <t>RT,(E-4B)</t>
@@ -106,7 +115,7 @@
     <t>TESTPACK ALAT TES</t>
   </si>
   <si>
-    <t>8</t>
+    <t>9</t>
   </si>
   <si>
     <t>10007241</t>
@@ -115,7 +124,7 @@
     <t>SENSITIF STRIP</t>
   </si>
   <si>
-    <t>9</t>
+    <t>10</t>
   </si>
   <si>
     <t>10013365</t>
@@ -124,7 +133,16 @@
     <t>AKURAT STRIP PCS</t>
   </si>
   <si>
-    <t>10</t>
+    <t>11</t>
+  </si>
+  <si>
+    <t>20141773</t>
+  </si>
+  <si>
+    <t>SUTRA KONDOM CINTA3S</t>
+  </si>
+  <si>
+    <t>12</t>
   </si>
   <si>
     <t>20088105</t>
@@ -206,9 +224,6 @@
   </si>
   <si>
     <t>SONY GIFT CARD 100K</t>
-  </si>
-  <si>
-    <t>12</t>
   </si>
   <si>
     <t>PT</t>
@@ -649,7 +664,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -817,15 +832,15 @@
         <v>27</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -834,10 +849,10 @@
         <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -857,7 +872,7 @@
         <v>34</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -877,7 +892,7 @@
         <v>37</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -891,13 +906,13 @@
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -911,21 +926,21 @@
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -934,38 +949,38 @@
         <v>23</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -974,18 +989,18 @@
         <v>23</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -994,18 +1009,18 @@
         <v>23</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -1014,18 +1029,18 @@
         <v>23</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -1034,18 +1049,18 @@
         <v>23</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -1054,18 +1069,18 @@
         <v>23</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -1074,18 +1089,18 @@
         <v>23</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -1094,18 +1109,18 @@
         <v>23</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -1114,18 +1129,18 @@
         <v>23</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -1134,10 +1149,10 @@
         <v>23</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>66</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1154,10 +1169,10 @@
         <v>23</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1174,10 +1189,10 @@
         <v>23</v>
       </c>
       <c r="E26" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F26" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1194,10 +1209,10 @@
         <v>23</v>
       </c>
       <c r="E27" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F27" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1217,15 +1232,15 @@
         <v>76</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>77</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>79</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
@@ -1237,26 +1252,66 @@
         <v>76</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>20</v>
+        <v>71</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="C30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C30" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>76</v>
-      </c>
       <c r="F30" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F32" s="1" t="s">
         <v>20</v>
       </c>
     </row>
